--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104686_W26.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104686_W26.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. GIEDRAITIS</t>
+          <t>M. HUERTAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3213</v>
+        <v>4.4692</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0426</v>
+        <v>7.7585</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.7212</v>
+        <v>-3.2894</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.5639</v>
+        <v>4.8864</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4417</v>
+        <v>3.4651</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.1222</v>
+        <v>1.4214</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4357</v>
+        <v>6.3014</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7721</v>
+        <v>4.1121</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6636</v>
+        <v>2.1893</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.9996</v>
+        <v>-1.415</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.2139</v>
+        <v>-0.6471</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.7858</v>
+        <v>-0.768</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8147</v>
+        <v>2.0487</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.4537</v>
+        <v>-0.2276</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3389</v>
+        <v>-0.9895</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3288</v>
+        <v>-0.1072</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9899</v>
+        <v>-0.8823</v>
       </c>
       <c r="V2" t="n">
-        <v>2.7317</v>
+        <v>-1.4764</v>
       </c>
       <c r="W2" t="n">
-        <v>2.7317</v>
+        <v>1.792</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. HUERTAS</t>
+          <t>B. FITIPALDO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2597</v>
+        <v>2.8639</v>
       </c>
       <c r="E3" t="n">
-        <v>6.9682</v>
+        <v>2.9191</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.7085</v>
+        <v>-0.0552</v>
       </c>
       <c r="G3" t="n">
-        <v>4.9049</v>
+        <v>1.0407</v>
       </c>
       <c r="H3" t="n">
-        <v>3.4895</v>
+        <v>-0.3447</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4154</v>
+        <v>1.3854</v>
       </c>
       <c r="J3" t="n">
-        <v>6.351</v>
+        <v>2.6849</v>
       </c>
       <c r="K3" t="n">
-        <v>4.152</v>
+        <v>-0.1002</v>
       </c>
       <c r="L3" t="n">
-        <v>2.199</v>
+        <v>2.7851</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.4461</v>
+        <v>-1.6442</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6626</v>
+        <v>-0.2446</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7835</v>
+        <v>-1.3997</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0415</v>
+        <v>0.6829</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2683</v>
+        <v>2.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.2084</v>
+        <v>-0.2647</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9557</v>
+        <v>0.195</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.2527</v>
+        <v>-0.4596</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.4783</v>
+        <v>1.405</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7997</v>
+        <v>1.405</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.278</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. FITIPALDO</t>
+          <t>R. GIEDRAITIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0768</v>
+        <v>2.6436</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4077</v>
+        <v>4.5479</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3309</v>
+        <v>-1.9043</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0371</v>
+        <v>-1.5562</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3463</v>
+        <v>-0.4314</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3834</v>
+        <v>-1.1248</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7024</v>
+        <v>1.4089</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.09370000000000001</v>
+        <v>0.7617</v>
       </c>
       <c r="L4" t="n">
-        <v>2.796</v>
+        <v>0.6473</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.6653</v>
+        <v>-2.9651</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2526</v>
+        <v>-1.1931</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.4126</v>
+        <v>-1.772</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6805</v>
+        <v>1.8211</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.361</v>
+        <v>-0.4553</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0415</v>
+        <v>2.2763</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0549</v>
+        <v>-0.345</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3478</v>
+        <v>0.8706</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7071</v>
+        <v>-1.2155</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4141</v>
+        <v>2.7237</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4141</v>
+        <v>2.7237</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2072</v>
+        <v>1.385</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6274</v>
+        <v>1.0377</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5799</v>
+        <v>0.3473</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6963</v>
+        <v>1.7026</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7229</v>
+        <v>1.7232</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0266</v>
+        <v>-0.0206</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7944</v>
+        <v>1.7864</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6451</v>
+        <v>1.6375</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.09810000000000001</v>
+        <v>-0.0838</v>
       </c>
       <c r="N5" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0857</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2395</v>
+        <v>-0.0673</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3297</v>
+        <v>0.095</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0901</v>
+        <v>-0.1623</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.1568</v>
+        <v>-1.1609</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7789</v>
+        <v>1.0025</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7796999999999999</v>
+        <v>-0.4921</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5585</v>
+        <v>1.4946</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5876</v>
+        <v>-0.5798</v>
       </c>
       <c r="H6" t="n">
-        <v>0.404</v>
+        <v>0.4076</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9915</v>
+        <v>-0.9874000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8522999999999999</v>
+        <v>-0.8728</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2007</v>
+        <v>0.1929</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.053</v>
+        <v>-1.0656</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2647</v>
+        <v>0.293</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2033</v>
+        <v>0.2148</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0614</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3802</v>
+        <v>-0.1705</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2994</v>
+        <v>0.6083</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6796</v>
+        <v>-0.7788</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="7">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3701</v>
+        <v>0.4369</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4088</v>
+        <v>1.3509</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0387</v>
+        <v>-0.9141</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8629</v>
+        <v>-0.8464</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6365</v>
+        <v>-0.6294</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2265</v>
+        <v>-0.2171</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5268</v>
+        <v>1.5161</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1834</v>
+        <v>0.1756</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3434</v>
+        <v>1.3405</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.3897</v>
+        <v>-2.3626</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8198</v>
+        <v>-0.805</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.5699</v>
+        <v>-1.5576</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5816</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1089</v>
+        <v>0.0624</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6905</v>
+        <v>-0.6002</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.341</v>
+        <v>-0.068</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4727</v>
+        <v>1.1035</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1316</v>
+        <v>-1.1715</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2553</v>
+        <v>2.2683</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4054</v>
+        <v>0.4104</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8499</v>
+        <v>1.8579</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1402</v>
+        <v>2.1349</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3117</v>
+        <v>0.3103</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8285</v>
+        <v>1.8246</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1151</v>
+        <v>0.1335</v>
       </c>
       <c r="N8" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1002</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0214</v>
+        <v>0.0333</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0611</v>
+        <v>-0.3575</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5081</v>
+        <v>0.1555</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.447</v>
+        <v>-0.513</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="9">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1168</v>
+        <v>-0.0843</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1218</v>
+        <v>-0.1222</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005</v>
+        <v>0.0378</v>
       </c>
       <c r="G9" t="n">
-        <v>0.316</v>
+        <v>0.3187</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1587</v>
+        <v>0.1607</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2986</v>
+        <v>0.3014</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1414</v>
+        <v>0.1435</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4328</v>
+        <v>-0.403</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2937</v>
+        <v>-0.2636</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. SCRUBB</t>
+          <t>W. VAN BECK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4556</v>
+        <v>-0.5122</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0975</v>
+        <v>-1.0257</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.553</v>
+        <v>0.5135</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2158</v>
+        <v>0.3415</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2105</v>
+        <v>0.1463</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0053</v>
+        <v>0.1952</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0481</v>
+        <v>0.0545</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.4932</v>
+        <v>0.0172</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4451</v>
+        <v>0.0372</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1676</v>
+        <v>0.287</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2828</v>
+        <v>0.129</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4504</v>
+        <v>0.1579</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9073</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3992</v>
+        <v>0.2845</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4386</v>
+        <v>0.2856</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0393</v>
+        <v>-0.0011</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>W. VAN BECK</t>
+          <t>T. SCRUBB</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.961</v>
+        <v>-1.1737</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3759</v>
+        <v>-0.3284</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4149</v>
+        <v>-0.8453000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3374</v>
+        <v>-1.2214</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1428</v>
+        <v>-1.2201</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1946</v>
+        <v>-0.0013</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0546</v>
+        <v>-1.0679</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0173</v>
+        <v>-1.5071</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0373</v>
+        <v>0.4392</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2828</v>
+        <v>-0.1535</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1255</v>
+        <v>0.287</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1573</v>
+        <v>-0.4405</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1642</v>
+        <v>-0.3181</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0696</v>
+        <v>0.037</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.3551</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. GUERRA</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5077</v>
+        <v>-1.9471</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3435</v>
+        <v>-0.1327</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.8512</v>
+        <v>-1.8144</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.0646</v>
+        <v>-2.9879</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2495</v>
+        <v>-1.781</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.8151</v>
+        <v>-1.2069</v>
       </c>
       <c r="J12" t="n">
-        <v>1.4019</v>
+        <v>-0.8109</v>
       </c>
       <c r="K12" t="n">
-        <v>1.2153</v>
+        <v>-0.6313</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1866</v>
+        <v>-0.1796</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.4665</v>
+        <v>-2.177</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.4648</v>
+        <v>-1.1497</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.0017</v>
+        <v>-1.0273</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.4952</v>
+        <v>-1.3658</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2427</v>
+        <v>-1.8211</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0907</v>
+        <v>-0.135</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.3335</v>
+        <v>-1.686</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2534</v>
+        <v>2.1789</v>
       </c>
       <c r="W12" t="n">
-        <v>2.3461</v>
+        <v>2.1789</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>F. GUERRA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.6014</v>
+        <v>-2.591</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6335</v>
+        <v>1.2587</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.9679</v>
+        <v>-3.8497</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.986</v>
+        <v>-2.0556</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.7865</v>
+        <v>-0.2553</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.1995</v>
+        <v>-1.8003</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.7804</v>
+        <v>1.382</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6203</v>
+        <v>1.1958</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1601</v>
+        <v>0.1862</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.2056</v>
+        <v>-3.4376</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.1662</v>
+        <v>-1.4511</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0395</v>
+        <v>-1.9865</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6805</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.361</v>
+        <v>-2.5039</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.4812</v>
+        <v>-1.3274</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6775</v>
+        <v>0.0439</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.8038</v>
+        <v>-1.3713</v>
       </c>
       <c r="V13" t="n">
-        <v>2.1853</v>
+        <v>1.2472</v>
       </c>
       <c r="W13" t="n">
-        <v>2.1853</v>
+        <v>2.3367</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.712499999999999</v>
+        <v>6.424799999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>17.4575</v>
+        <v>17.8752</v>
       </c>
       <c r="F14" t="n">
-        <v>-11.7447</v>
+        <v>-11.4507</v>
       </c>
       <c r="G14" t="n">
-        <v>1.266199999999998</v>
+        <v>1.310899999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>1.652300000000001</v>
+        <v>1.651400000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3861000000000001</v>
+        <v>-0.3406000000000007</v>
       </c>
       <c r="J14" t="n">
-        <v>14.7435</v>
+        <v>14.5347</v>
       </c>
       <c r="K14" t="n">
-        <v>6.3077</v>
+        <v>6.181699999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>8.435699999999999</v>
+        <v>8.353099999999998</v>
       </c>
       <c r="M14" t="n">
-        <v>-13.4773</v>
+        <v>-13.2239</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.655399999999999</v>
+        <v>-4.530400000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-8.821900000000001</v>
+        <v>-8.6938</v>
       </c>
       <c r="P14" t="n">
-        <v>6.804900000000002</v>
+        <v>6.8289</v>
       </c>
       <c r="Q14" t="n">
-        <v>-10.2074</v>
+        <v>-10.2433</v>
       </c>
       <c r="R14" t="n">
-        <v>17.0124</v>
+        <v>17.0724</v>
       </c>
       <c r="S14" t="n">
-        <v>-6.9863</v>
+        <v>-6.3174</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2551</v>
+        <v>1.9717</v>
       </c>
       <c r="U14" t="n">
-        <v>-8.2417</v>
+        <v>-8.2888</v>
       </c>
       <c r="V14" t="n">
-        <v>4.628</v>
+        <v>4.602</v>
       </c>
       <c r="W14" t="n">
-        <v>11.6662</v>
+        <v>11.6121</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.0382</v>
+        <v>-7.010000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. MARTINEZ</t>
+          <t>P. VILDOZA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4413</v>
+        <v>3.5765</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8768</v>
+        <v>3.0959</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4355</v>
+        <v>0.4806</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1674</v>
+        <v>2.4486</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1515</v>
+        <v>0.7524</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.3189</v>
+        <v>1.6962</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9418</v>
+        <v>1.8021</v>
       </c>
       <c r="K15" t="n">
-        <v>3.3177</v>
+        <v>0.3652</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.3759</v>
+        <v>1.4369</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.1092</v>
+        <v>0.6465</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1662</v>
+        <v>0.3871</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.9431</v>
+        <v>0.2593</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1342</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>0.6829</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7675</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4548</v>
+        <v>0.4806</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3127</v>
+        <v>0.2407</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7071</v>
+        <v>1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>0.7071</v>
+        <v>2.1789</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. VILDOZA</t>
+          <t>S. MARTINEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.793</v>
+        <v>3.128</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3003</v>
+        <v>4.4978</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4927</v>
+        <v>-1.3698</v>
       </c>
       <c r="G16" t="n">
-        <v>2.4562</v>
+        <v>-0.1642</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7503</v>
+        <v>2.1458</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7059</v>
+        <v>-2.31</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8238</v>
+        <v>2.9155</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3739</v>
+        <v>3.2955</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4499</v>
+        <v>-0.38</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6324</v>
+        <v>-3.0797</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3764</v>
+        <v>-1.1497</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2559</v>
+        <v>-1.93</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.07530000000000001</v>
+        <v>1.4516</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3478</v>
+        <v>1.1074</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2725</v>
+        <v>0.3441</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0927</v>
+        <v>0.7025</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1853</v>
+        <v>0.7025</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. HILDRETH</t>
+          <t>M. SUSINSKAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0048</v>
+        <v>-0.1541</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7278</v>
+        <v>1.0006</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.723</v>
+        <v>-1.1547</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1575</v>
+        <v>1.0374</v>
       </c>
       <c r="H17" t="n">
-        <v>0.723</v>
+        <v>0.5996</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4345</v>
+        <v>0.4379</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8507</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1416</v>
+        <v>0.9308</v>
       </c>
       <c r="L17" t="n">
-        <v>0.709</v>
+        <v>-0.2388</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3069</v>
+        <v>0.3454</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5814</v>
+        <v>-0.3312</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2745</v>
+        <v>0.6766</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4202</v>
+        <v>-0.0825</v>
       </c>
       <c r="T17" t="n">
-        <v>2.0113</v>
+        <v>0.5362</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4089</v>
+        <v>-0.6187</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.3461</v>
+        <v>-1.792</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.3461</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. MARIC</t>
+          <t>C. HILDRETH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1194</v>
+        <v>-0.23</v>
       </c>
       <c r="E18" t="n">
-        <v>1.054</v>
+        <v>0.5325</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9346</v>
+        <v>-0.7624</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1873</v>
+        <v>1.1521</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4619</v>
+        <v>0.7156</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2745</v>
+        <v>0.4365</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8241000000000001</v>
+        <v>0.8347</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8241000000000001</v>
+        <v>0.1272</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.7075</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6368</v>
+        <v>0.3174</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3622</v>
+        <v>0.5884</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6805</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9340000000000001</v>
+        <v>1.1823</v>
       </c>
       <c r="T18" t="n">
-        <v>1.364</v>
+        <v>0.8359</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4301</v>
+        <v>0.3463</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3214</v>
+        <v>-2.3367</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3214</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. GEBEN</t>
+          <t>M. HUGHES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1794</v>
+        <v>-0.353</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6119</v>
+        <v>-0.0408</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7913</v>
+        <v>-0.3122</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.648</v>
+        <v>-2.0055</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8874</v>
+        <v>-0.2786</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.5354</v>
+        <v>-1.7269</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8245</v>
+        <v>-1.8058</v>
       </c>
       <c r="K19" t="n">
-        <v>1.5341</v>
+        <v>0.1239</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2904</v>
+        <v>-1.9298</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.4725</v>
+        <v>-0.1997</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.4025</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.8258</v>
+        <v>0.2028</v>
       </c>
       <c r="P19" t="n">
-        <v>-4.3098</v>
+        <v>1.1382</v>
       </c>
       <c r="Q19" t="n">
-        <v>-5.6708</v>
+        <v>-0.2276</v>
       </c>
       <c r="R19" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S19" t="n">
-        <v>3.525</v>
+        <v>0.5144</v>
       </c>
       <c r="T19" t="n">
-        <v>2.6585</v>
+        <v>0.9032</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8665</v>
+        <v>-0.3888</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.7997</v>
+        <v>1.0895</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5463</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. HUGHES</t>
+          <t>D. NEEDHAM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2625</v>
+        <v>-0.4241</v>
       </c>
       <c r="E20" t="n">
-        <v>0.09950000000000001</v>
+        <v>4.8567</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.362</v>
+        <v>-5.2807</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.9952</v>
+        <v>1.9487</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2785</v>
+        <v>-1.2178</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7167</v>
+        <v>3.1664</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.7825</v>
+        <v>5.2007</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1314</v>
+        <v>-0.3695</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.914</v>
+        <v>5.5702</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2126</v>
+        <v>-3.2521</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4099</v>
+        <v>-0.8483000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1973</v>
+        <v>-2.4037</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1342</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2268</v>
+        <v>-2.5039</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5985</v>
+        <v>1.2403</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0162</v>
+        <v>1.0704</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4177</v>
+        <v>0.1699</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.792</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. BRUNOT</t>
+          <t>N. MARIC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6586</v>
+        <v>-0.6433</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1391</v>
+        <v>0.2163</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5195</v>
+        <v>-0.8596</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3622</v>
+        <v>0.1833</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5195</v>
+        <v>0.4542</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1573</v>
+        <v>-0.271</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.8134</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>0.8134</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3622</v>
+        <v>-0.6301</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5195</v>
+        <v>-0.3592</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1573</v>
+        <v>-0.271</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2964</v>
+        <v>0.1718</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1391</v>
+        <v>0.5411</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1573</v>
+        <v>-0.3692</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. NEEDHAM</t>
+          <t>K. BRUNOT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8826000000000001</v>
+        <v>-0.6565</v>
       </c>
       <c r="E22" t="n">
-        <v>4.7859</v>
+        <v>-0.1394</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.6685</v>
+        <v>-0.5171</v>
       </c>
       <c r="G22" t="n">
-        <v>1.9594</v>
+        <v>-0.3592</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2179</v>
+        <v>-0.5171</v>
       </c>
       <c r="I22" t="n">
-        <v>3.1772</v>
+        <v>0.1579</v>
       </c>
       <c r="J22" t="n">
-        <v>5.2418</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3503</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>5.5921</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.2824</v>
+        <v>-0.3592</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8675</v>
+        <v>-0.5171</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.4149</v>
+        <v>0.1579</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.8147</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.4952</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7724</v>
+        <v>-0.2973</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9467</v>
+        <v>-0.1394</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1742</v>
+        <v>-0.1579</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.7997</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.8924</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6613</v>
+        <v>-1.3963</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.7468</v>
+        <v>-1.517</v>
       </c>
       <c r="F23" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.1207</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.4553</v>
+        <v>-1.4578</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7675999999999999</v>
+        <v>-0.7696</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6877</v>
+        <v>-0.6882</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.5381</v>
+        <v>-1.5448</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7517</v>
+        <v>-0.7552</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0828</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="O23" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6596</v>
+        <v>-0.3937</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2087</v>
+        <v>0.0278</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4509</v>
+        <v>-0.4215</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. SUSINSKAS</t>
+          <t>M. GEBEN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.8166</v>
+        <v>-1.6918</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2862</v>
+        <v>-0.6176</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.5304</v>
+        <v>-1.0742</v>
       </c>
       <c r="G24" t="n">
-        <v>1.0269</v>
+        <v>-0.6546</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5871</v>
+        <v>0.8875</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4398</v>
+        <v>-1.542</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7058</v>
+        <v>1.795</v>
       </c>
       <c r="K24" t="n">
-        <v>0.9351</v>
+        <v>1.5201</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.2293</v>
+        <v>0.2749</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3211</v>
+        <v>-2.4496</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.348</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>0.6691</v>
+        <v>-1.8169</v>
       </c>
       <c r="P24" t="n">
-        <v>0.6805</v>
+        <v>-4.325</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.2268</v>
+        <v>-5.6908</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.7242</v>
+        <v>2.0405</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7652</v>
+        <v>1.4862</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9591</v>
+        <v>0.5543</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.7997</v>
+        <v>1.2472</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.792</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.7997</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P. BUSQUETS</t>
+          <t>O. LIVINGSTON</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.573</v>
+        <v>-2.7662</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.6821</v>
+        <v>1.0042</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.8909</v>
+        <v>-3.7704</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.6379</v>
+        <v>-0.7987</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.7071</v>
+        <v>-1.7232</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0692</v>
+        <v>0.9246</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.2909</v>
+        <v>2.8418</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.3995</v>
+        <v>-0.1142</v>
       </c>
       <c r="L25" t="n">
-        <v>1.1087</v>
+        <v>2.9559</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.347</v>
+        <v>-3.6405</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.3075</v>
+        <v>-1.6091</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.0395</v>
+        <v>-2.0314</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R25" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S25" t="n">
-        <v>0.5205</v>
+        <v>0.4877</v>
       </c>
       <c r="T25" t="n">
-        <v>0.8771</v>
+        <v>0.4387</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3566</v>
+        <v>0.049</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.3214</v>
+        <v>-1.0895</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.3214</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>O. LIVINGSTON</t>
+          <t>P. BUSQUETS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.0371</v>
+        <v>-3.3271</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0179</v>
+        <v>-1.5961</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.0191</v>
+        <v>-1.731</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.7874</v>
+        <v>-2.641</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.7229</v>
+        <v>-2.7001</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9355</v>
+        <v>0.0591</v>
       </c>
       <c r="J26" t="n">
-        <v>2.8764</v>
+        <v>-0.3205</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.1008</v>
+        <v>-1.4069</v>
       </c>
       <c r="L26" t="n">
-        <v>2.9772</v>
+        <v>1.0864</v>
       </c>
       <c r="M26" t="n">
-        <v>-3.6638</v>
+        <v>-2.3205</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.6221</v>
+        <v>-1.2932</v>
       </c>
       <c r="O26" t="n">
-        <v>-2.0417</v>
+        <v>-1.0273</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R26" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.796</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6261</v>
+        <v>1.0007</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.17</v>
+        <v>-0.2331</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.0927</v>
+        <v>-0.3155</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.0927</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.712599999999998</v>
+        <v>-4.937900000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>11.5841</v>
+        <v>11.2931</v>
       </c>
       <c r="F27" t="n">
-        <v>-17.2966</v>
+        <v>-16.2308</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.2661</v>
+        <v>-1.3109</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.6523</v>
+        <v>-1.6513</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3862</v>
+        <v>0.3404999999999996</v>
       </c>
       <c r="J27" t="n">
-        <v>13.4774</v>
+        <v>13.2241</v>
       </c>
       <c r="K27" t="n">
-        <v>4.6556</v>
+        <v>4.5303</v>
       </c>
       <c r="L27" t="n">
-        <v>8.8217</v>
+        <v>8.6936</v>
       </c>
       <c r="M27" t="n">
-        <v>-14.7433</v>
+        <v>-14.5351</v>
       </c>
       <c r="N27" t="n">
-        <v>-6.307699999999999</v>
+        <v>-6.1818</v>
       </c>
       <c r="O27" t="n">
-        <v>-8.4358</v>
+        <v>-8.353300000000001</v>
       </c>
       <c r="P27" t="n">
-        <v>-6.804899999999999</v>
+        <v>-6.8289</v>
       </c>
       <c r="Q27" t="n">
-        <v>-17.0124</v>
+        <v>-17.0723</v>
       </c>
       <c r="R27" t="n">
-        <v>10.2075</v>
+        <v>10.2435</v>
       </c>
       <c r="S27" t="n">
-        <v>6.986600000000002</v>
+        <v>7.804</v>
       </c>
       <c r="T27" t="n">
-        <v>8.241700000000002</v>
+        <v>8.2888</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.2553</v>
+        <v>-0.4849</v>
       </c>
       <c r="V27" t="n">
-        <v>-4.627800000000001</v>
+        <v>-4.602</v>
       </c>
       <c r="W27" t="n">
-        <v>6.8775</v>
+        <v>6.852399999999999</v>
       </c>
       <c r="X27" t="n">
-        <v>-11.5054</v>
+        <v>-11.4543</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104686_W26.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104686_W26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104686_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104686_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104686_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104686_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104686_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104686_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104686_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104686_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104686_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104686_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104686_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104686_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-7.010000000000001</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104686_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104686_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104686_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104686_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104686_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104686_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104686_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104686_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104686_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104686_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104686_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104686_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-11.4543</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
